--- a/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -54,15 +54,6 @@
     <t>support</t>
   </si>
   <si>
-    <t>animal</t>
-  </si>
-  <si>
-    <t>breaking</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
     <t>engine</t>
   </si>
   <si>
@@ -75,28 +66,13 @@
     <t>horn</t>
   </si>
   <si>
-    <t>horse</t>
-  </si>
-  <si>
     <t>impact</t>
   </si>
   <si>
-    <t>music</t>
-  </si>
-  <si>
     <t>shout</t>
   </si>
   <si>
-    <t>sigh</t>
-  </si>
-  <si>
     <t>skidding</t>
-  </si>
-  <si>
-    <t>speech</t>
-  </si>
-  <si>
-    <t>tick_tock</t>
   </si>
   <si>
     <t>tire_squeal</t>
@@ -484,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -518,25 +494,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>5</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -556,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -570,25 +546,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -596,25 +572,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.312</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0.476</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -637,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -648,25 +624,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -677,19 +653,19 @@
         <v>1</v>
       </c>
       <c r="C8">
+        <v>0.333</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -712,220 +688,12 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-      <c r="H10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>0.333</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
         <v>5</v>
       </c>
     </row>
@@ -941,31 +709,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -973,7 +741,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>93</v>
@@ -982,7 +750,7 @@
         <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1002,7 +770,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>132</v>
@@ -1011,7 +779,7 @@
         <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1038,31 +806,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1070,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>95</v>
@@ -1079,7 +847,7 @@
         <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1099,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>189</v>
@@ -1108,7 +876,7 @@
         <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1135,31 +903,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1167,7 +935,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>88</v>
@@ -1176,7 +944,7 @@
         <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1196,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>169</v>
@@ -1205,7 +973,7 @@
         <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1232,31 +1000,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1264,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>19</v>
@@ -1273,7 +1041,7 @@
         <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1293,7 +1061,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>73</v>
@@ -1301,17 +1069,8 @@
       <c r="D3">
         <v>79</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>120</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1322,7 +1081,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>79</v>
@@ -1330,17 +1089,8 @@
       <c r="D4">
         <v>109</v>
       </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>120</v>
-      </c>
       <c r="H4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1358,31 +1108,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1390,7 +1140,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -1399,7 +1149,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1419,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1428,7 +1178,7 @@
         <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1448,7 +1198,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>63</v>
@@ -1457,7 +1207,7 @@
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>60</v>
@@ -1484,31 +1234,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1516,7 +1266,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1525,7 +1275,7 @@
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1545,7 +1295,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1554,7 +1304,7 @@
         <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1574,7 +1324,7 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>74</v>
@@ -1583,7 +1333,7 @@
         <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>60</v>
@@ -1610,31 +1360,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1642,7 +1392,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1650,17 +1400,8 @@
       <c r="D2">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>60</v>
-      </c>
       <c r="H2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1671,7 +1412,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -1679,17 +1420,8 @@
       <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>60</v>
-      </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1707,31 +1439,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1739,7 +1471,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1747,17 +1479,8 @@
       <c r="D2">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>180</v>
-      </c>
       <c r="H2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1768,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>44</v>
@@ -1776,17 +1499,8 @@
       <c r="D3">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>180</v>
-      </c>
       <c r="H3">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1804,31 +1518,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1836,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1844,17 +1558,8 @@
       <c r="D2">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
       <c r="H2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1865,7 +1570,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -1873,17 +1578,8 @@
       <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>120</v>
-      </c>
       <c r="H3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1901,31 +1597,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1933,7 +1629,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>96</v>
@@ -1941,17 +1637,8 @@
       <c r="D2">
         <v>105</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
       <c r="H2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1962,7 +1649,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>116</v>
@@ -1971,7 +1658,7 @@
         <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>120</v>
@@ -1998,31 +1685,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2030,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -2039,7 +1726,7 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -2066,31 +1753,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2098,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -2107,7 +1794,7 @@
         <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>120</v>
@@ -2134,31 +1821,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2166,7 +1853,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -2175,7 +1862,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2202,31 +1889,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2234,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>37</v>
@@ -2243,19 +1930,19 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>60</v>
       </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
       <c r="H2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -1353,6 +1359,378 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>122</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>108</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>120</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>120</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>102</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>35</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>182</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
@@ -1422,6 +1800,191 @@
       </c>
       <c r="H3">
         <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>32</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>103</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>60</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>

--- a/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w2_5s_h2_5s.xlsx
@@ -500,19 +500,19 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>0</v>
